--- a/shadowedhistory/flashpoints/series_log.xlsx
+++ b/shadowedhistory/flashpoints/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3622,6 +3622,336 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-10 22:44</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/9611f52bd6fe47fe184592199bdb723e_1789080225.mp4</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep31/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-10 22:46</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/66318a278b60da1e83ebbb0bfbf6423c_1789080349.mp4</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep31/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:44</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/0e0a022ac3a0c289225971d0706f74f6_1789166621.mp4</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep31/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:47</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/939df522b38ae130acdf578e89ca6a77_1789166743.mp4</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep31/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:29</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/43a11646bdae380e0e953197bbaf3fa8_1789252108.mp4</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep31/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:32</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/11fcaf2a1edbc47f9daeb8b2cd16e46c_1789252234.mp4</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep31/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
